--- a/customers.xlsx
+++ b/customers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lucit-my.sharepoint.com/personal/jouko_teeriaho_lapinamk_fi/Documents/Työpöytä/Probability/2_Statistics/Statistics25/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lucit-my.sharepoint.com/personal/jouko_teeriaho_lapinamk_fi/Documents/Tiedostot/GitHub/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{131A3226-F30C-42BA-A4F3-4B9B589CE064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65BE353A-775D-4FAA-B51F-6EBF27956487}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{131A3226-F30C-42BA-A4F3-4B9B589CE064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31D1E725-EC69-47D5-BB6A-2DE4B1212EAF}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="80" windowWidth="19110" windowHeight="10000" xr2:uid="{2E0E04A6-E858-429D-A294-47240510E5EA}"/>
+    <workbookView xWindow="330" yWindow="840" windowWidth="18870" windowHeight="9960" xr2:uid="{2E0E04A6-E858-429D-A294-47240510E5EA}"/>
   </bookViews>
   <sheets>
     <sheet name="customer research" sheetId="2" r:id="rId1"/>
@@ -543,22 +543,22 @@
     <col min="5" max="5" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A5" s="4" t="s">
         <v>0</v>
       </c>
@@ -569,7 +569,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>8</v>
       </c>
@@ -580,7 +580,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>7</v>
       </c>
@@ -591,7 +591,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -602,7 +602,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>2</v>
       </c>
@@ -610,7 +610,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>5</v>
       </c>
@@ -618,7 +618,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>6</v>
       </c>
@@ -629,7 +629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>9</v>
       </c>
@@ -640,7 +640,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>6</v>
       </c>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>8</v>
       </c>
@@ -656,15 +656,19 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>3</v>
       </c>
       <c r="B15" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E15" s="1">
+        <f>_xlfn.T.TEST(A6:A23,B6:B27,1,2)</f>
+        <v>1.8262630412137549E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>7</v>
       </c>
@@ -745,8 +749,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B27" s="6">
-        <f ca="1">MIN(ROUND(_xlfn.NORM.INV(RAND(),7.5,2.4),0),10)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
@@ -755,8 +758,8 @@
         <v>6.1111111111111107</v>
       </c>
       <c r="B29" s="1">
-        <f ca="1">AVERAGE(B6:B28)</f>
-        <v>7.8181818181818183</v>
+        <f>AVERAGE(B6:B28)</f>
+        <v>7.8636363636363633</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
@@ -767,5 +770,14 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Aptos"&amp;10&amp;K000000 Luottamuksellinen - Confidential (3Y)&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{d823ee79-bdbf-4d11-a783-980929fd6733}" enabled="1" method="Standard" siteId="{4c60a66f-0a8d-446e-9ac0-836a00d84542}" removed="0"/>
+</clbl:labelList>
 </file>
--- a/customers.xlsx
+++ b/customers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lucit-my.sharepoint.com/personal/jouko_teeriaho_lapinamk_fi/Documents/Tiedostot/GitHub/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{131A3226-F30C-42BA-A4F3-4B9B589CE064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31D1E725-EC69-47D5-BB6A-2DE4B1212EAF}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{BD250176-F063-4813-988A-569157E4C978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB9C98A5-B847-43A3-922A-BAD515161C36}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="840" windowWidth="18870" windowHeight="9960" xr2:uid="{2E0E04A6-E858-429D-A294-47240510E5EA}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="16150" windowHeight="9960" xr2:uid="{2E0E04A6-E858-429D-A294-47240510E5EA}"/>
   </bookViews>
   <sheets>
     <sheet name="customer research" sheetId="2" r:id="rId1"/>
@@ -536,29 +536,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D440A1E-9241-4C1F-9688-86A636370402}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
     <col min="5" max="5" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A5" s="4" t="s">
         <v>0</v>
       </c>
@@ -569,7 +569,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>8</v>
       </c>
@@ -580,7 +580,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>7</v>
       </c>
@@ -591,7 +591,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -602,7 +602,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>2</v>
       </c>
@@ -610,7 +610,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>5</v>
       </c>
@@ -618,7 +618,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>6</v>
       </c>
@@ -629,7 +629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>9</v>
       </c>
@@ -640,7 +640,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>6</v>
       </c>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>8</v>
       </c>
@@ -656,19 +656,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>3</v>
       </c>
       <c r="B15" s="6">
         <v>8</v>
       </c>
-      <c r="E15" s="1">
-        <f>_xlfn.T.TEST(A6:A23,B6:B27,1,2)</f>
-        <v>1.8262630412137549E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>7</v>
       </c>
@@ -676,15 +672,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>5</v>
       </c>
       <c r="B17" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="D17">
+        <f>_xlfn.T.TEST(A6:A23,B6:B27,1,2)</f>
+        <v>1.0745336699915747E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>6</v>
       </c>
@@ -692,7 +692,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>9</v>
       </c>
@@ -700,7 +700,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>4</v>
       </c>
@@ -708,7 +708,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>9</v>
       </c>
@@ -716,7 +716,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>4</v>
       </c>
@@ -724,7 +724,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>6</v>
       </c>
@@ -732,52 +732,63 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B24" s="6">
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B25" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="E25" s="1">
+        <f>(B29-A29)/SQRT(A31^2/18+B31^2/22)</f>
+        <v>3.1477642922269147</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B26" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B27" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="7">
         <f>AVERAGE(A6:A28)</f>
         <v>6.1111111111111107</v>
       </c>
       <c r="B29" s="1">
         <f>AVERAGE(B6:B28)</f>
-        <v>7.8636363636363633</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <f>_xlfn.STDEV.S(A6:A23)</f>
+        <v>2.0548046676563261</v>
+      </c>
+      <c r="B31">
+        <f>_xlfn.STDEV.S(B6:B23)</f>
+        <v>1.6617574758359674</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;R&amp;"Aptos"&amp;10&amp;K000000 Luottamuksellinen - Confidential (3Y)&amp;1#_x000D_</oddHeader>
-  </headerFooter>
 </worksheet>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{d823ee79-bdbf-4d11-a783-980929fd6733}" enabled="1" method="Standard" siteId="{4c60a66f-0a8d-446e-9ac0-836a00d84542}" removed="0"/>
+  <clbl:label id="{d823ee79-bdbf-4d11-a783-980929fd6733}" enabled="1" method="Standard" siteId="{4c60a66f-0a8d-446e-9ac0-836a00d84542}" contentBits="1" removed="0"/>
 </clbl:labelList>
 </file>
--- a/customers.xlsx
+++ b/customers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lucit-my.sharepoint.com/personal/jouko_teeriaho_lapinamk_fi/Documents/Tiedostot/GitHub/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{BD250176-F063-4813-988A-569157E4C978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB9C98A5-B847-43A3-922A-BAD515161C36}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{BD250176-F063-4813-988A-569157E4C978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6269AB2B-0A50-485D-9C09-468CF3E14F01}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="16150" windowHeight="9960" xr2:uid="{2E0E04A6-E858-429D-A294-47240510E5EA}"/>
+    <workbookView xWindow="2280" yWindow="120" windowWidth="16150" windowHeight="9960" xr2:uid="{2E0E04A6-E858-429D-A294-47240510E5EA}"/>
   </bookViews>
   <sheets>
     <sheet name="customer research" sheetId="2" r:id="rId1"/>
@@ -672,19 +672,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>5</v>
       </c>
       <c r="B17" s="6">
         <v>10</v>
       </c>
-      <c r="D17">
-        <f>_xlfn.T.TEST(A6:A23,B6:B27,1,2)</f>
-        <v>1.0745336699915747E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>6</v>
       </c>
@@ -692,7 +688,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>9</v>
       </c>
@@ -700,7 +696,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>4</v>
       </c>
@@ -708,7 +704,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>9</v>
       </c>
@@ -716,7 +712,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>4</v>
       </c>
@@ -724,7 +720,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>6</v>
       </c>
@@ -732,31 +728,27 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B24" s="6">
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B25" s="6">
         <v>8</v>
       </c>
-      <c r="E25" s="1">
-        <f>(B29-A29)/SQRT(A31^2/18+B31^2/22)</f>
-        <v>3.1477642922269147</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B26" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B27" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="7">
         <f>AVERAGE(A6:A28)</f>
         <v>6.1111111111111107</v>
@@ -766,12 +758,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31">
         <f>_xlfn.STDEV.S(A6:A23)</f>
         <v>2.0548046676563261</v>
@@ -789,6 +781,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{d823ee79-bdbf-4d11-a783-980929fd6733}" enabled="1" method="Standard" siteId="{4c60a66f-0a8d-446e-9ac0-836a00d84542}" contentBits="1" removed="0"/>
+  <clbl:label id="{d823ee79-bdbf-4d11-a783-980929fd6733}" enabled="1" method="Standard" siteId="{4c60a66f-0a8d-446e-9ac0-836a00d84542}" removed="0"/>
 </clbl:labelList>
 </file>
--- a/customers.xlsx
+++ b/customers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lucit-my.sharepoint.com/personal/jouko_teeriaho_lapinamk_fi/Documents/Tiedostot/GitHub/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{BD250176-F063-4813-988A-569157E4C978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6269AB2B-0A50-485D-9C09-468CF3E14F01}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{BD250176-F063-4813-988A-569157E4C978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AC06C9F-95CC-4508-909A-85D13E49F43C}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="120" windowWidth="16150" windowHeight="9960" xr2:uid="{2E0E04A6-E858-429D-A294-47240510E5EA}"/>
+    <workbookView xWindow="1850" yWindow="310" windowWidth="16150" windowHeight="9960" xr2:uid="{2E0E04A6-E858-429D-A294-47240510E5EA}"/>
   </bookViews>
   <sheets>
     <sheet name="customer research" sheetId="2" r:id="rId1"/>
@@ -217,6 +217,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -536,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D440A1E-9241-4C1F-9688-86A636370402}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -761,16 +765,6 @@
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <f>_xlfn.STDEV.S(A6:A23)</f>
-        <v>2.0548046676563261</v>
-      </c>
-      <c r="B31">
-        <f>_xlfn.STDEV.S(B6:B23)</f>
-        <v>1.6617574758359674</v>
       </c>
     </row>
   </sheetData>
